--- a/doc/_static/example-files/PMHC-4-1-combined.xlsx
+++ b/doc/_static/example-files/PMHC-4-1-combined.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10413"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jennib/Work/git/PMHC/spec/doc/_static/example-files/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E858E875-B898-A943-87EB-B202E9B954B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -22,7 +28,7 @@
     <sheet name="Service Contact Practitioners" sheetId="13" r:id="rId13"/>
     <sheet name="Practitioners" sheetId="14" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1091,8 +1097,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1129,13 +1135,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1173,7 +1187,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1207,6 +1221,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1241,9 +1256,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1416,11 +1432,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1428,7 +1444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1436,12 +1452,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -1450,11 +1466,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1486,7 +1502,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1515,7 +1531,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1544,7 +1560,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1573,7 +1589,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1602,7 +1618,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1631,7 +1647,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1660,7 +1676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1689,7 +1705,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1718,7 +1734,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1747,7 +1763,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1782,11 +1798,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:BB22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:54">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1950,7 +1966,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="2" spans="1:54">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2111,7 +2127,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:54">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2272,7 +2288,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:54">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2433,7 +2449,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:54">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -2594,7 +2610,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:54">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -2755,7 +2771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:54">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2916,7 +2932,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:54">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -3077,7 +3093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:54">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3238,7 +3254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:54">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -3399,7 +3415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:54">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -3560,7 +3576,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:54">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -3721,7 +3737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:54">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -3882,7 +3898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:54">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -4043,7 +4059,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:54">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -4204,7 +4220,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:54">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -4365,7 +4381,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:53">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -4526,7 +4542,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:53">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -4687,7 +4703,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:53">
+    <row r="19" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -4848,7 +4864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:53">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -5009,7 +5025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:53">
+    <row r="21" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -5170,7 +5186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:53">
+    <row r="22" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -5337,11 +5353,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:S11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -5400,7 +5416,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -5456,7 +5472,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -5512,7 +5528,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -5568,7 +5584,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -5624,7 +5640,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -5680,7 +5696,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -5736,7 +5752,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -5792,7 +5808,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -5848,7 +5864,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -5904,7 +5920,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -5966,11 +5982,11 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -5987,7 +6003,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -6004,7 +6020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -6021,7 +6037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -6038,7 +6054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -6055,7 +6071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -6072,7 +6088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -6089,7 +6105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -6106,7 +6122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -6123,7 +6139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -6140,7 +6156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6157,7 +6173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -6174,7 +6190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -6197,11 +6213,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -6230,7 +6246,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -6256,7 +6272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -6282,7 +6298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -6308,7 +6324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -6334,7 +6350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -6360,7 +6376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -6386,7 +6402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -6412,7 +6428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -6438,7 +6454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -6464,7 +6480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6496,11 +6512,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -6535,7 +6551,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -6570,11 +6586,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -6609,7 +6625,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -6641,7 +6657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -6673,7 +6689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -6705,7 +6721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -6737,7 +6753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -6769,7 +6785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -6807,11 +6823,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -6855,7 +6871,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -6896,7 +6912,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -6937,7 +6953,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -6978,7 +6994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -7019,7 +7035,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -7051,7 +7067,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -7083,7 +7099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -7124,7 +7140,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -7156,7 +7172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -7188,7 +7204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -7220,7 +7236,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -7258,11 +7274,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -7309,7 +7325,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7353,7 +7369,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -7397,7 +7413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -7441,7 +7457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -7485,7 +7501,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -7529,7 +7545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -7573,7 +7589,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -7617,7 +7633,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -7661,7 +7677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -7705,7 +7721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -7749,7 +7765,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -7799,11 +7815,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AD11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -7895,7 +7911,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7984,7 +8000,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -8076,7 +8092,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -8165,7 +8181,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -8254,7 +8270,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -8343,7 +8359,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -8429,7 +8445,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -8518,7 +8534,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -8607,7 +8623,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -8696,7 +8712,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -8788,11 +8804,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>140</v>
       </c>
@@ -8806,7 +8822,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -8820,7 +8836,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -8834,7 +8850,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -8848,7 +8864,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -8862,7 +8878,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -8876,7 +8892,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -8890,7 +8906,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -8904,7 +8920,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -8918,7 +8934,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -8932,7 +8948,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -8952,11 +8968,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -8976,7 +8992,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -8993,7 +9009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -9010,7 +9026,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -9027,7 +9043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -9044,7 +9060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -9061,7 +9077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -9078,7 +9094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -9095,7 +9111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -9112,7 +9128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -9129,7 +9145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -9146,7 +9162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -9163,7 +9179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -9180,7 +9196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -9197,7 +9213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -9214,7 +9230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -9231,7 +9247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -9248,7 +9264,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -9265,7 +9281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -9282,7 +9298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -9299,7 +9315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -9316,7 +9332,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -9339,11 +9355,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -9402,7 +9418,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -9458,7 +9474,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -9514,7 +9530,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -9570,7 +9586,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -9626,7 +9642,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
